--- a/01_Input/00_CO Validation/Chad - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Chad - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27010"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/yacin_kouadio_undp_org/Documents/UNDP CHAD/PROGRAMME/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{98942119-6D57-F24D-A1B6-B6AEDF138E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13D4D76A-3B9C-4E2C-9874-852C85D58C16}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{98942119-6D57-F24D-A1B6-B6AEDF138E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB72509B-5D5A-40F0-9BD9-F3F0443A8B22}"/>
   <bookViews>
     <workbookView xWindow="2320" yWindow="500" windowWidth="18160" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -373,7 +376,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -461,12 +464,105 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -597,6 +693,42 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -621,80 +753,119 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1004,295 +1175,289 @@
   <dimension ref="A1:R9"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="5" customWidth="1"/>
-    <col min="2" max="3" width="41.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="35" style="4" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="65.140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="5"/>
-    <col min="12" max="12" width="48.42578125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="5"/>
-    <col min="14" max="14" width="18.5703125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" style="5" customWidth="1"/>
-    <col min="16" max="17" width="9.140625" style="5"/>
-    <col min="18" max="18" width="25" style="5" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="15.7109375" style="72" customWidth="1"/>
+    <col min="2" max="3" width="41.7109375" style="72" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="92" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="72" customWidth="1"/>
+    <col min="6" max="6" width="35" style="82" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="94" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" style="82" customWidth="1"/>
+    <col min="9" max="9" width="65.140625" style="82" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" style="72" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="72"/>
+    <col min="12" max="12" width="48.42578125" style="72" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="72"/>
+    <col min="14" max="14" width="18.5703125" style="72" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" style="72" customWidth="1"/>
+    <col min="16" max="17" width="9.140625" style="72"/>
+    <col min="18" max="18" width="25" style="72" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="72"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="71" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="41" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A2" s="68">
+    <row r="2" spans="1:18" ht="31.5" customHeight="1">
+      <c r="A2" s="73">
         <v>135028</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="71">
+      <c r="D2" s="76">
         <v>1745000</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G2" s="79">
         <v>0</v>
       </c>
-      <c r="H2" s="39">
+      <c r="H2" s="80">
         <v>7.85E-2</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="N2" s="80" t="s">
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="N2" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="80" t="s">
+      <c r="O2" s="82" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="30.75">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="23" t="s">
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="79">
         <v>0</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="N3" s="80" t="s">
+      <c r="I3" s="81"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="N3" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="80" t="s">
+      <c r="O3" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-    </row>
-    <row r="4" spans="1:18" s="41" customFormat="1" ht="60.75">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="36" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="60.75">
+      <c r="A4" s="102"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="43">
+      <c r="G4" s="84">
         <v>0</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="83">
         <v>150</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="45"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-    </row>
-    <row r="5" spans="1:18" s="41" customFormat="1" ht="30.75">
-      <c r="A5" s="72"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="36" t="s">
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="86"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+    </row>
+    <row r="5" spans="1:18" ht="30.75">
+      <c r="A5" s="102"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="79">
         <v>0</v>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="87">
         <v>15000</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="I5" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="45"/>
-      <c r="N5" s="80" t="s">
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="86"/>
+      <c r="N5" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="80" t="s">
+      <c r="O5" s="82" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="60.75">
-      <c r="A6" s="72"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="23" t="s">
+      <c r="A6" s="102"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="84">
         <v>0</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="89">
         <v>50</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="47"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="45"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-    </row>
-    <row r="7" spans="1:18" s="41" customFormat="1" ht="30.75">
-      <c r="A7" s="72"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="36" t="s">
+      <c r="J6" s="90"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="86"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+    </row>
+    <row r="7" spans="1:18" ht="30.75">
+      <c r="A7" s="102"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="79">
         <v>0</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="45"/>
-      <c r="N7" s="80" t="s">
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="86"/>
+      <c r="N7" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="80" t="s">
+      <c r="O7" s="82" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="41" customFormat="1" ht="30.75">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="36" t="s">
+    <row r="8" spans="1:18" ht="30.75">
+      <c r="A8" s="104"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="79">
         <v>0</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="83">
         <v>198</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="45"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="80"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="86"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="82"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="B9" s="4"/>
-      <c r="C9" s="12"/>
-      <c r="G9" s="11"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="91"/>
+      <c r="G9" s="93"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -1408,16 +1573,16 @@
       </c>
     </row>
     <row r="2" spans="1:19" s="41" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="65">
+      <c r="A2" s="48">
         <v>135028</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="56">
+      <c r="D2" s="57">
         <v>1745000</v>
       </c>
       <c r="E2" s="36" t="s">
@@ -1446,10 +1611,10 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="66"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="57"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="58"/>
       <c r="E3" s="23" t="s">
         <v>25</v>
       </c>
@@ -1477,10 +1642,10 @@
       <c r="S3" s="41"/>
     </row>
     <row r="4" spans="1:19" s="41" customFormat="1" ht="60.75">
-      <c r="A4" s="66"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="57"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="58"/>
       <c r="E4" s="36" t="s">
         <v>29</v>
       </c>
@@ -1501,10 +1666,10 @@
       <c r="L4" s="45"/>
     </row>
     <row r="5" spans="1:19" s="41" customFormat="1" ht="30.75">
-      <c r="A5" s="66"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="57"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="36" t="s">
         <v>32</v>
       </c>
@@ -1531,10 +1696,10 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="60.75">
-      <c r="A6" s="66"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="57"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="23" t="s">
         <v>35</v>
       </c>
@@ -1560,10 +1725,10 @@
       <c r="S6" s="41"/>
     </row>
     <row r="7" spans="1:19" s="41" customFormat="1">
-      <c r="A7" s="66"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="57"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="36" t="s">
         <v>25</v>
       </c>
@@ -1590,10 +1755,10 @@
       </c>
     </row>
     <row r="8" spans="1:19" s="41" customFormat="1" ht="30.75">
-      <c r="A8" s="67"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="58"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="59"/>
       <c r="E8" s="36" t="s">
         <v>41</v>
       </c>
@@ -1708,16 +1873,16 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.95">
-      <c r="A2" s="49">
+      <c r="A2" s="61">
         <v>135028</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="51">
+      <c r="D2" s="63">
         <v>1745000</v>
       </c>
       <c r="E2" s="13" t="s">
@@ -1737,10 +1902,10 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="49"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
       <c r="E3" s="13" t="s">
         <v>25</v>
       </c>
@@ -1756,10 +1921,10 @@
       <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:9" ht="63.95">
-      <c r="A4" s="49"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="51"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="13" t="s">
         <v>20</v>
       </c>
@@ -1777,10 +1942,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="32.1">
-      <c r="A5" s="49"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="13" t="s">
         <v>32</v>
       </c>
@@ -1798,10 +1963,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="63.95">
-      <c r="A6" s="49"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="51"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="63"/>
       <c r="E6" s="13" t="s">
         <v>35</v>
       </c>
@@ -1819,10 +1984,10 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.95">
-      <c r="A7" s="49"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="51"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63"/>
       <c r="E7" s="13" t="s">
         <v>41</v>
       </c>
@@ -1840,10 +2005,10 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="32.1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="63"/>
       <c r="E8" s="13" t="s">
         <v>41</v>
       </c>
@@ -1913,7 +2078,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="64" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
@@ -1924,7 +2089,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="52"/>
+      <c r="A3" s="64"/>
       <c r="B3" t="s">
         <v>20</v>
       </c>
@@ -1933,7 +2098,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="52"/>
+      <c r="A4" s="64"/>
       <c r="B4" t="s">
         <v>32</v>
       </c>
@@ -1942,7 +2107,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="65" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
@@ -1953,7 +2118,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="53"/>
+      <c r="A6" s="65"/>
       <c r="B6" t="s">
         <v>53</v>
       </c>
@@ -1962,7 +2127,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="53"/>
+      <c r="A7" s="65"/>
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -1971,7 +2136,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="53"/>
+      <c r="A8" s="65"/>
       <c r="B8" t="s">
         <v>57</v>
       </c>
@@ -1980,7 +2145,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="53"/>
+      <c r="A9" s="65"/>
       <c r="B9" t="s">
         <v>41</v>
       </c>
@@ -1989,7 +2154,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="66" t="s">
         <v>60</v>
       </c>
       <c r="B10" t="s">
@@ -2000,7 +2165,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="54"/>
+      <c r="A11" s="66"/>
       <c r="B11" t="s">
         <v>63</v>
       </c>
@@ -2009,7 +2174,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="67" t="s">
         <v>65</v>
       </c>
       <c r="B12" t="s">
@@ -2020,7 +2185,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="55"/>
+      <c r="A13" s="67"/>
       <c r="B13" t="s">
         <v>29</v>
       </c>
@@ -2029,7 +2194,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="55"/>
+      <c r="A14" s="67"/>
       <c r="B14" t="s">
         <v>69</v>
       </c>
@@ -2080,17 +2245,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2339,14 +2493,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA903917-B6F3-48D5-8E13-468762282C8C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA903917-B6F3-48D5-8E13-468762282C8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
--- a/01_Input/00_CO Validation/Chad - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Chad - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28224"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/yacin_kouadio_undp_org/Documents/UNDP CHAD/PROGRAMME/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{98942119-6D57-F24D-A1B6-B6AEDF138E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57A81601-8548-4469-97A0-AE675A1C2D5B}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{98942119-6D57-F24D-A1B6-B6AEDF138E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85895E0F-4155-4F8D-BEFA-671497113687}"/>
   <bookViews>
-    <workbookView xWindow="2320" yWindow="500" windowWidth="18160" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2320" yWindow="500" windowWidth="18160" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>Project ID</t>
   </si>
@@ -119,79 +119,85 @@
     <t>MW</t>
   </si>
   <si>
+    <t xml:space="preserve">1 minigrid with a capacity of 78.5 kW is  installed and oprationnal </t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Energy Access</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <t>Number of households receiving electricity from the mini grid</t>
+  </si>
+  <si>
+    <t>750 HH</t>
+  </si>
+  <si>
+    <t>750HH with a total of 4500 persons</t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t>Number of private entrepreneurs supported and equipped with renewable energy solutions for the development of economical activities</t>
+  </si>
+  <si>
+    <t>78 young entrepreneurs were powered by solar panels (30 720W)</t>
+  </si>
+  <si>
+    <t>Clean Cooking</t>
+  </si>
+  <si>
+    <t>Number of personnes supplied with domestic energy solutions for cooking</t>
+  </si>
+  <si>
+    <t>1530 people received biogas, improved stoves and solar cookers.</t>
+  </si>
+  <si>
+    <t>Agriculture and Food System</t>
+  </si>
+  <si>
+    <t>Number of women's and young's groups supported and equipped with renewable energy solutions for the development agriculture</t>
+  </si>
+  <si>
+    <t>20 women's groups and 10 youth groups are supported by solar pumped water wells for the development of agricultural activities (14 000W)</t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Number of solar lamps supplied</t>
+  </si>
+  <si>
+    <t>1000 HH</t>
+  </si>
+  <si>
+    <t>877 solar lamps are provided to the population</t>
+  </si>
+  <si>
+    <t>Number of people supported by the solar dryers</t>
+  </si>
+  <si>
+    <t>198 people were supported by solar dryers</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
     <t>1 minigrid with a capacity of 78.5 kW is about to be installed</t>
-  </si>
-  <si>
-    <t>Non-VF</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Energy Access</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Electricity Access</t>
-  </si>
-  <si>
-    <t>Number of households receiving electricity from the mini grid</t>
-  </si>
-  <si>
-    <t>750 HH</t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t>Number of private entrepreneurs supported and equipped with renewable energy solutions for the development of economical activities</t>
-  </si>
-  <si>
-    <t>78 young entrepreneurs were powered by solar panels (30 720W)</t>
-  </si>
-  <si>
-    <t>Clean Cooking</t>
-  </si>
-  <si>
-    <t>Number of personnes supplied with domestic energy solutions for cooking</t>
-  </si>
-  <si>
-    <t>1530 people received biogas, improved stoves and solar cookers.</t>
-  </si>
-  <si>
-    <t>Agriculture and Food System</t>
-  </si>
-  <si>
-    <t>Number of women's and young's groups supported and equipped with renewable energy solutions for the development agriculture</t>
-  </si>
-  <si>
-    <t>20 women's groups and 10 youth groups are supported by solar pumped water wells for the development of agricultural activities (14 000W)</t>
-  </si>
-  <si>
-    <t>Energy Infrastructure Services</t>
-  </si>
-  <si>
-    <t>Number of solar lamps supplied</t>
-  </si>
-  <si>
-    <t>1000 HH</t>
-  </si>
-  <si>
-    <t>877 solar lamps are provided to the population</t>
-  </si>
-  <si>
-    <t>Number of people supported by the solar dryers</t>
-  </si>
-  <si>
-    <t>198 people were supported by solar dryers</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
   </si>
   <si>
     <t>Renewable Energy</t>
@@ -802,6 +808,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -850,7 +857,6 @@
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1172,7 +1178,7 @@
     <col min="2" max="3" width="41.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" style="7" customWidth="1"/>
     <col min="5" max="5" width="28.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="35" style="1" customWidth="1"/>
+    <col min="6" max="6" width="46.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.85546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="20.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="65.140625" style="1" customWidth="1"/>
@@ -1220,7 +1226,7 @@
       <c r="I1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="99" t="s">
+      <c r="J1" s="83" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="72" t="s">
@@ -1327,9 +1333,13 @@
       <c r="H3" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="52"/>
+      <c r="I3" s="52" t="s">
+        <v>34</v>
+      </c>
       <c r="J3" s="52"/>
-      <c r="K3" s="30"/>
+      <c r="K3" s="30">
+        <v>55</v>
+      </c>
       <c r="L3" s="80" t="s">
         <v>27</v>
       </c>
@@ -1356,10 +1366,10 @@
       <c r="C4" s="61"/>
       <c r="D4" s="67"/>
       <c r="E4" s="30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="54">
         <v>0</v>
@@ -1368,10 +1378,12 @@
         <v>150</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" s="55"/>
-      <c r="K4" s="30"/>
+      <c r="K4" s="30">
+        <v>30</v>
+      </c>
       <c r="L4" s="80" t="s">
         <v>27</v>
       </c>
@@ -1394,10 +1406,10 @@
       <c r="C5" s="61"/>
       <c r="D5" s="67"/>
       <c r="E5" s="30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="50">
         <v>0</v>
@@ -1406,7 +1418,7 @@
         <v>15000</v>
       </c>
       <c r="I5" s="55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" s="55"/>
       <c r="K5" s="30"/>
@@ -1432,10 +1444,10 @@
       <c r="C6" s="61"/>
       <c r="D6" s="67"/>
       <c r="E6" s="30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="54">
         <v>0</v>
@@ -1444,10 +1456,12 @@
         <v>50</v>
       </c>
       <c r="I6" s="55" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" s="55"/>
-      <c r="K6" s="44"/>
+      <c r="K6" s="44">
+        <v>0.6</v>
+      </c>
       <c r="L6" s="80" t="s">
         <v>27</v>
       </c>
@@ -1470,22 +1484,24 @@
       <c r="C7" s="61"/>
       <c r="D7" s="67"/>
       <c r="E7" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="50">
         <v>0</v>
       </c>
       <c r="H7" s="53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7" s="52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7" s="52"/>
-      <c r="K7" s="30"/>
+      <c r="K7" s="30">
+        <v>40</v>
+      </c>
       <c r="L7" s="80" t="s">
         <v>27</v>
       </c>
@@ -1508,10 +1524,10 @@
       <c r="C8" s="70"/>
       <c r="D8" s="71"/>
       <c r="E8" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="50">
         <v>0</v>
@@ -1520,10 +1536,12 @@
         <v>198</v>
       </c>
       <c r="I8" s="52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" s="52"/>
-      <c r="K8" s="30"/>
+      <c r="K8" s="30">
+        <v>90</v>
+      </c>
       <c r="L8" s="80" t="s">
         <v>27</v>
       </c>
@@ -1658,10 +1676,10 @@
         <v>10</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" s="19" t="s">
         <v>13</v>
@@ -1680,16 +1698,16 @@
       </c>
     </row>
     <row r="2" spans="1:19" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="83">
+      <c r="A2" s="84">
         <v>135028</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="92">
+      <c r="D2" s="93">
         <v>1745000</v>
       </c>
       <c r="E2" s="33" t="s">
@@ -1705,7 +1723,7 @@
         <v>7.85E-2</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J2" s="33"/>
       <c r="K2" s="33"/>
@@ -1714,14 +1732,14 @@
         <v>28</v>
       </c>
       <c r="P2" s="38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="84"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="93"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="20" t="s">
         <v>31</v>
       </c>
@@ -1739,7 +1757,7 @@
       <c r="K3" s="30"/>
       <c r="L3" s="30"/>
       <c r="O3" s="38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P3" s="38" t="s">
         <v>31</v>
@@ -1749,15 +1767,15 @@
       <c r="S3" s="38"/>
     </row>
     <row r="4" spans="1:19" s="38" customFormat="1" ht="60.75">
-      <c r="A4" s="84"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="93"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="40">
         <v>0</v>
@@ -1766,22 +1784,22 @@
         <v>150</v>
       </c>
       <c r="I4" s="41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" s="33"/>
       <c r="K4" s="33"/>
       <c r="L4" s="42"/>
     </row>
     <row r="5" spans="1:19" s="38" customFormat="1" ht="30.75">
-      <c r="A5" s="84"/>
-      <c r="B5" s="87"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="93"/>
+      <c r="A5" s="85"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="94"/>
       <c r="E5" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="35">
         <v>0</v>
@@ -1790,28 +1808,28 @@
         <v>15000</v>
       </c>
       <c r="I5" s="41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" s="33"/>
       <c r="K5" s="33"/>
       <c r="L5" s="42"/>
       <c r="O5" s="38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="60.75">
-      <c r="A6" s="84"/>
-      <c r="B6" s="87"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="93"/>
+      <c r="A6" s="85"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="24">
         <v>0</v>
@@ -1820,7 +1838,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" s="44"/>
       <c r="K6" s="30"/>
@@ -1832,45 +1850,45 @@
       <c r="S6" s="38"/>
     </row>
     <row r="7" spans="1:19" s="38" customFormat="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="93"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="94"/>
       <c r="E7" s="33" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="35">
         <v>0</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7" s="33"/>
       <c r="K7" s="33"/>
       <c r="L7" s="42"/>
       <c r="O7" s="38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P7" s="38" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="38" customFormat="1" ht="30.75">
-      <c r="A8" s="85"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="94"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="95"/>
       <c r="E8" s="33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="35">
         <v>0</v>
@@ -1879,7 +1897,7 @@
         <v>198</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" s="33"/>
       <c r="K8" s="33"/>
@@ -1980,23 +1998,23 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.95">
-      <c r="A2" s="96">
+      <c r="A2" s="97">
         <v>135028</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="98">
+      <c r="D2" s="99">
         <v>1745000</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2" s="11">
         <v>0</v>
@@ -2005,14 +2023,14 @@
         <v>2</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="96"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="99"/>
       <c r="E3" s="10" t="s">
         <v>31</v>
       </c>
@@ -2028,15 +2046,15 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" ht="63.95">
-      <c r="A4" s="96"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="98"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="99"/>
       <c r="E4" s="10" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="13">
         <v>0</v>
@@ -2045,19 +2063,19 @@
         <v>150</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="32.1">
-      <c r="A5" s="96"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="99"/>
       <c r="E5" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="11">
         <v>0</v>
@@ -2066,19 +2084,19 @@
         <v>15000</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="63.95">
-      <c r="A6" s="96"/>
-      <c r="B6" s="95"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="98"/>
+      <c r="A6" s="97"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="99"/>
       <c r="E6" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="13">
         <v>0</v>
@@ -2087,19 +2105,19 @@
         <v>50</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.95">
-      <c r="A7" s="96"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="98"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="99"/>
       <c r="E7" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="11">
         <v>0</v>
@@ -2108,19 +2126,19 @@
         <v>1000</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="32.1">
-      <c r="A8" s="96"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="98"/>
+      <c r="A8" s="97"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="99"/>
       <c r="E8" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="11">
         <v>0</v>
@@ -2129,7 +2147,7 @@
         <v>150</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2185,7 +2203,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2193,143 +2211,143 @@
         <v>24</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="100" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45.75">
       <c r="A6" s="100" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30.75">
       <c r="A7" s="100" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30.75">
       <c r="A8" s="100" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30.75">
       <c r="A9" s="100" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="100" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10" s="101" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="100" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="101" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30.75">
       <c r="A12" s="100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="100" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" s="101" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="100" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14" s="101" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="100" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B15" s="101" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="100" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="101" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="100" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="101" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
       <c r="A19" s="100" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B19" s="101" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="100" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" s="101" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
@@ -2337,15 +2355,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="102" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="100" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B22" s="101" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2354,8 +2372,60 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Komenan Yacin Kouadio</DisplayName>
+        <AccountId>1786</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jos De La Haye</DisplayName>
+        <AccountId>2565</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fungai Matura</DisplayName>
+        <AccountId>1028</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Tannya Quinza-armenta</DisplayName>
+        <AccountId>2508</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2380,6 +2450,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2459,6 +2530,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2602,28 +2678,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA903917-B6F3-48D5-8E13-468762282C8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2631,5 +2687,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9552F8E0-2B10-44B4-81B5-92DAF2A4FD97}"/>
 </file>
--- a/01_Input/00_CO Validation/Chad - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Chad - Energy Projects.xlsx
@@ -1492,7 +1492,7 @@
       <c r="K9" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="R2:R8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -1522,12 +1522,6 @@
     </dataValidation>
     <dataValidation sqref="Q2:Q8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
